--- a/data/Zorg_en_Hoop_monthly.xlsx
+++ b/data/Zorg_en_Hoop_monthly.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\OneDrive\Documents\Data_Website\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B644A852-F6B7-4496-A462-4C5A6D08D3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5A2543-ABF8-49CF-B121-C49FE525751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4645E167-86B9-4E45-866C-5B881B13017F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4645E167-86B9-4E45-866C-5B881B13017F}"/>
   </bookViews>
   <sheets>
     <sheet name="data_products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_products!$A$1:$C$777</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -893,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B716C3A-09DE-493B-8CA8-22DE291B800F}">
-  <dimension ref="A1:C777"/>
+  <dimension ref="A1:C784"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9443,6 +9459,83 @@
         <v>161</v>
       </c>
     </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A778">
+        <v>2026</v>
+      </c>
+      <c r="B778">
+        <v>1</v>
+      </c>
+      <c r="C778" s="1">
+        <v>151.80000000000001</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A779">
+        <v>2026</v>
+      </c>
+      <c r="B779">
+        <v>2</v>
+      </c>
+      <c r="C779" s="1">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A780">
+        <v>2026</v>
+      </c>
+      <c r="B780">
+        <v>3</v>
+      </c>
+      <c r="C780" s="1">
+        <v>253.8</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A781">
+        <v>2026</v>
+      </c>
+      <c r="B781">
+        <v>4</v>
+      </c>
+      <c r="C781" s="1">
+        <v>252.4</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A782">
+        <v>2026</v>
+      </c>
+      <c r="B782">
+        <v>5</v>
+      </c>
+      <c r="C782" s="1">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A783">
+        <v>2026</v>
+      </c>
+      <c r="B783">
+        <v>6</v>
+      </c>
+      <c r="C783" s="1">
+        <v>408.9</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A784">
+        <v>2026</v>
+      </c>
+      <c r="B784">
+        <v>7</v>
+      </c>
+      <c r="C784" s="1">
+        <v>110.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
